--- a/data/updates.xlsx
+++ b/data/updates.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>م</t>
   </si>
@@ -62,6 +62,48 @@
   </si>
   <si>
     <t>144f076e-0d21-4fa1-b453-5ff64898f905</t>
+  </si>
+  <si>
+    <t>15n16788a10</t>
+  </si>
+  <si>
+    <t>ملازم مصطفى محسن هادي</t>
+  </si>
+  <si>
+    <t>معيدة</t>
+  </si>
+  <si>
+    <t>كتيبة اتصالات قيادة الدفاع الجوي</t>
+  </si>
+  <si>
+    <t>التاجي</t>
+  </si>
+  <si>
+    <t>7:33:29 م</t>
+  </si>
+  <si>
+    <t>2b91b6a6-9a22-4ed1-8b59-3405b7a1ba17</t>
+  </si>
+  <si>
+    <t>2345674567</t>
+  </si>
+  <si>
+    <t>محمد</t>
+  </si>
+  <si>
+    <t>محمول بعجلة</t>
+  </si>
+  <si>
+    <t>يبلات</t>
+  </si>
+  <si>
+    <t>نملات</t>
+  </si>
+  <si>
+    <t>7:34:39 م</t>
+  </si>
+  <si>
+    <t>89936979-8cb2-400f-b60b-fd1af42a5e76</t>
   </si>
 </sst>
 </file>
@@ -94,7 +136,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,6 +161,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE2C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EDFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
@@ -176,6 +233,15 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -517,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -588,6 +654,64 @@
         <v>16</v>
       </c>
     </row>
+    <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
